--- a/samples_csv/double.xlsx
+++ b/samples_csv/double.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Relative\Projects\seva projects\badminton\society-badminton-app\samples_csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B07F64-A231-4319-A161-DF2FDEFDF1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F37BD8C-2F3D-49F6-8F01-4E7DFC874F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1474" yWindow="1474" windowWidth="18515" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3326" yWindow="1431" windowWidth="18514" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Doubles" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>MHT Id</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>Abhist Pal</t>
+  </si>
+  <si>
+    <t>partner's mhtid</t>
   </si>
 </sst>
 </file>
@@ -251,7 +254,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -274,14 +277,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -594,15 +609,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultColWidth="11.4609375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.69140625" customWidth="1"/>
     <col min="2" max="2" width="20.84375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,8 +628,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D1" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>119420</v>
       </c>
@@ -624,7 +643,7 @@
         <v>8469091699</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>126888</v>
       </c>
@@ -635,7 +654,7 @@
         <v>8879939998</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>129694</v>
       </c>
@@ -646,7 +665,7 @@
         <v>9426242325</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>133348</v>
       </c>
@@ -657,7 +676,7 @@
         <v>9016255414</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>135304</v>
       </c>
@@ -668,7 +687,7 @@
         <v>9638565431</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>135596</v>
       </c>
@@ -679,7 +698,7 @@
         <v>9924629232</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>138340</v>
       </c>
@@ -690,7 +709,7 @@
         <v>7046894277</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>143412</v>
       </c>
@@ -701,7 +720,7 @@
         <v>7405811791</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>144635</v>
       </c>
@@ -712,7 +731,7 @@
         <v>8087700757</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>146170</v>
       </c>
@@ -723,7 +742,7 @@
         <v>6353232254</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>150538</v>
       </c>
@@ -734,7 +753,7 @@
         <v>9171213176</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>151148</v>
       </c>
@@ -745,7 +764,7 @@
         <v>9552612512</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>151693</v>
       </c>
@@ -756,7 +775,7 @@
         <v>7096493425</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>151918</v>
       </c>
@@ -767,7 +786,7 @@
         <v>9316630864</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>152061</v>
       </c>
